--- a/Board/BOM/1.1/TeslaBMBCheck.xlsx
+++ b/Board/BOM/1.1/TeslaBMBCheck.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\svpet\Nextcloud\Elektronik\Projects\TeslaBMBCheck\Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\svpet\Nextcloud\Elektronik\Projects\TeslaBMBCheck\Board\BOM\1.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>Qty</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Crystal:Crystal_SMD_HC49-SD</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -816,7 +819,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:H28" totalsRowShown="0">
   <autoFilter ref="A1:H28"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="C1,C3,C4"/>
+    <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Qty"/>
     <tableColumn id="3" name="Value" dataDxfId="0"/>
     <tableColumn id="4" name="DNP"/>
@@ -1105,7 +1108,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1131,7 +1134,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -1145,7 +1148,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1159,7 +1162,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1173,7 +1176,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1187,7 +1190,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1201,7 +1204,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1215,7 +1218,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1229,7 +1232,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1246,7 +1249,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1260,7 +1263,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1274,7 +1277,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1288,7 +1291,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1305,7 +1308,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1322,7 +1325,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1339,7 +1342,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1353,7 +1356,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -1367,7 +1370,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -1381,7 +1384,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1395,7 +1398,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -1409,7 +1412,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1423,7 +1426,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1437,7 +1440,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1451,7 +1454,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -1463,7 +1466,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1480,7 +1483,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1497,7 +1500,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1510,6 +1513,9 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
       <c r="B28">
         <v>1</v>
       </c>
@@ -1522,8 +1528,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>